--- a/db/site_db_2026-10-09.xlsx
+++ b/db/site_db_2026-10-09.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12 08:40:08</t>
+          <t>2026-10-12 08:45:14</t>
         </is>
       </c>
     </row>
